--- a/State lab test results/SDVL_Results.xlsx
+++ b/State lab test results/SDVL_Results.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alex/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alex/Documents/GitHub/BackyardBirds/State lab test results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CFA8C65-545A-F241-A7F3-2A31FCCCC789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C666E7E-A7E3-7F44-94A2-21B49A8FA758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3080" yWindow="2160" windowWidth="28040" windowHeight="17180" xr2:uid="{BE4D56C9-88CE-FE4C-A4D2-BDDE1F9C4E21}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Results" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="52">
   <si>
     <t>USGS#,Soil_ID</t>
   </si>
@@ -164,9 +164,6 @@
     <t>Pseudomonas alvei</t>
   </si>
   <si>
-    <t>3171-38516</t>
-  </si>
-  <si>
     <t>LEEBF-S3</t>
   </si>
   <si>
@@ -180,13 +177,28 @@
   </si>
   <si>
     <t>WEAGLECONPace-E</t>
+  </si>
+  <si>
+    <t>3171-38516-S2</t>
+  </si>
+  <si>
+    <t>Pseudomonas koreensis</t>
+  </si>
+  <si>
+    <t>Klebsiella aerogenes</t>
+  </si>
+  <si>
+    <t>Citrobacter freundii</t>
+  </si>
+  <si>
+    <t>Enterobacter sp.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -206,6 +218,12 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -252,12 +270,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1050,7 +1069,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B25" s="1">
         <v>45820</v>
@@ -1061,10 +1080,16 @@
       <c r="D25" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="E25" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B26" s="1">
         <v>45854</v>
@@ -1075,10 +1100,13 @@
       <c r="D26" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="E26" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B27" s="1">
         <v>45853</v>
@@ -1089,10 +1117,16 @@
       <c r="D27" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="E27" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B28" s="1">
         <v>45853</v>
@@ -1103,10 +1137,16 @@
       <c r="D28" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="E28" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B29" s="1">
         <v>45853</v>
@@ -1117,10 +1157,16 @@
       <c r="D29" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="E29" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B30" s="1">
         <v>45853</v>
@@ -1131,6 +1177,12 @@
       <c r="D30" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="E30" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C31" s="2" t="s">
@@ -1139,5 +1191,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/State lab test results/SDVL_Results.xlsx
+++ b/State lab test results/SDVL_Results.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alex/Documents/GitHub/BackyardBirds/State lab test results/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kelseymccune/Documents/GitHub/BackyardBirds/State lab test results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C666E7E-A7E3-7F44-94A2-21B49A8FA758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08B9FE51-E050-1D42-BBC4-C74C1747F7CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3080" yWindow="2160" windowWidth="28040" windowHeight="17180" xr2:uid="{BE4D56C9-88CE-FE4C-A4D2-BDDE1F9C4E21}"/>
+    <workbookView xWindow="3080" yWindow="2120" windowWidth="28040" windowHeight="17180" xr2:uid="{BE4D56C9-88CE-FE4C-A4D2-BDDE1F9C4E21}"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="49">
   <si>
     <t>USGS#,Soil_ID</t>
   </si>
@@ -164,6 +164,9 @@
     <t>Pseudomonas alvei</t>
   </si>
   <si>
+    <t>3171-38516</t>
+  </si>
+  <si>
     <t>LEEBF-S3</t>
   </si>
   <si>
@@ -179,26 +182,14 @@
     <t>WEAGLECONPace-E</t>
   </si>
   <si>
-    <t>3171-38516-S2</t>
-  </si>
-  <si>
-    <t>Pseudomonas koreensis</t>
-  </si>
-  <si>
-    <t>Klebsiella aerogenes</t>
-  </si>
-  <si>
-    <t>Citrobacter freundii</t>
-  </si>
-  <si>
-    <t>Enterobacter sp.</t>
+    <t>Quadrant</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -218,12 +209,6 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Helvetica"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -270,13 +255,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -611,586 +595,555 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AF13019-09B0-754C-80A6-F57B33F3CD61}">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.83203125" customWidth="1"/>
-    <col min="2" max="3" width="16.33203125" customWidth="1"/>
-    <col min="4" max="4" width="26.33203125" customWidth="1"/>
-    <col min="6" max="6" width="19.6640625" customWidth="1"/>
+    <col min="1" max="2" width="22.83203125" customWidth="1"/>
+    <col min="3" max="4" width="16.33203125" customWidth="1"/>
+    <col min="5" max="5" width="26.33203125" customWidth="1"/>
+    <col min="7" max="7" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2">
+      <c r="C2" s="2">
         <v>45953</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2">
+      <c r="C3" s="2">
         <v>45967</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2">
+      <c r="C4" s="2">
         <v>45967</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2">
+      <c r="C5" s="2">
         <v>45967</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="1">
+      <c r="C6" s="1">
         <v>45980</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="1">
+      <c r="C7" s="1">
         <v>45980</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="1">
+      <c r="C8" s="1">
         <v>45980</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="2">
+      <c r="C9" s="2">
         <v>45981</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="2">
+      <c r="C10" s="2">
         <v>45821</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="2">
+      <c r="C11" s="2">
         <v>45821</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="D11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="2">
+      <c r="C12" s="2">
         <v>45805</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="D12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="2">
+      <c r="C13" s="2">
         <v>45855</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="D13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="2">
+      <c r="C14" s="2">
         <v>45848</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="D14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" t="s">
         <v>28</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="2">
+      <c r="C15" s="2">
         <v>45848</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="D15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" t="s">
         <v>28</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="2">
+      <c r="C16" s="2">
         <v>45848</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="D16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" t="s">
         <v>28</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="2">
+      <c r="C17" s="2">
         <v>45848</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="D17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" t="s">
         <v>28</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="2">
+      <c r="C18" s="2">
         <v>45820</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="D18" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="2">
+      <c r="C19" s="2">
         <v>45821</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="D19" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="G19" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="2">
+      <c r="C20" s="2">
         <v>45820</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="D20" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="G20" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="2">
+      <c r="C21" s="2">
         <v>45820</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="G21" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="1">
+      <c r="C22" s="1">
         <v>45854</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="D22" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="G22" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
-      <c r="B23" s="2">
+      <c r="C23" s="2">
         <v>45821</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="D23" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="G23" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>35</v>
       </c>
-      <c r="B24" s="2">
+      <c r="C24" s="2">
         <v>45848</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="D24" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="G24" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" s="1">
+        <v>45820</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="1">
+        <v>45854</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" s="1">
+        <v>45853</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" s="1">
+        <v>45853</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" s="1">
+        <v>45853</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
         <v>47</v>
       </c>
-      <c r="B25" s="1">
-        <v>45820</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>42</v>
-      </c>
-      <c r="B26" s="1">
-        <v>45854</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>43</v>
-      </c>
-      <c r="B27" s="1">
+      <c r="C30" s="1">
         <v>45853</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>44</v>
-      </c>
-      <c r="B28" s="1">
-        <v>45853</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>45</v>
-      </c>
-      <c r="B29" s="1">
-        <v>45853</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>46</v>
-      </c>
-      <c r="B30" s="1">
-        <v>45853</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="D30" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C31" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D31" s="2" t="s">
         <v>18</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>